--- a/test/res/item.xlsx
+++ b/test/res/item.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\bite\Desktop\github\xlsx-exporter\test\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E90600-7D28-474A-996D-65D980CFD1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C8289F-9F0A-480B-92F2-8FC7E0783B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5625" yWindow="780" windowWidth="19185" windowHeight="20070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37620" yWindow="885" windowWidth="29610" windowHeight="20070" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="config" sheetId="2" r:id="rId1"/>
     <sheet name="item" sheetId="1" r:id="rId2"/>
     <sheet name="follow" sheetId="3" r:id="rId3"/>
+    <sheet name="none" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">config!$A$2:$G$13</definedName>
@@ -49,6 +50,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>需要可堆叠才能入包</t>
         </r>
@@ -60,6 +63,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>1 绿色
 2 蓝色
@@ -76,6 +81,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Administrator:
 </t>
@@ -84,6 +91,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">{money_id = xxx}对应money表的道具
 {hero_id = xxx}对应hero表的角色
@@ -99,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="101">
   <si>
     <t>id</t>
   </si>
@@ -402,6 +411,10 @@
   </si>
   <si>
     <t>@config;@stringify(merge);@typedef</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -409,7 +422,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -441,11 +454,15 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -456,6 +473,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -563,7 +588,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -631,11 +656,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -955,13 +981,13 @@
       <c r="A1" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
@@ -1823,7 +1849,7 @@
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="23" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1927,4 +1953,20 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADBB972E-C927-480C-A467-3665FD9F033A}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B2" s="24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/test/res/item.xlsx
+++ b/test/res/item.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\bite\Desktop\github\xlsx-exporter\test\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C8289F-9F0A-480B-92F2-8FC7E0783B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A789DBAA-9DBD-46B0-A534-EB87F9C9C1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37620" yWindow="885" windowWidth="29610" windowHeight="20070" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4950" yWindow="420" windowWidth="29610" windowHeight="19950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="config" sheetId="2" r:id="rId1"/>
     <sheet name="item" sheetId="1" r:id="rId2"/>
     <sheet name="follow" sheetId="3" r:id="rId3"/>
-    <sheet name="none" sheetId="4" r:id="rId4"/>
+    <sheet name="map" sheetId="5" r:id="rId4"/>
+    <sheet name="none" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">config!$A$2:$G$13</definedName>
@@ -108,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="113">
   <si>
     <t>id</t>
   </si>
@@ -407,27 +408,80 @@
   </si>
   <si>
     <t>!@follow(name)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>@config;@stringify(merge);@typedef</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>s</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>kind</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>auto</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试2</t>
+  </si>
+  <si>
+    <t>测试21</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试22</t>
+  </si>
+  <si>
+    <t>@map(kind,level)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>@config;@stringify;@typedef</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -487,7 +541,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -548,6 +602,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -584,90 +644,103 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -978,16 +1051,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="A1" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
@@ -1373,7 +1446,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1794,9 +1867,9 @@
       <c r="J13" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="75"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1947,26 +2020,193 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="A1:A13">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E27B46D-4699-4B1C-B2B1-8A327D06725E}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.5" customWidth="1"/>
+    <col min="2" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="11.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="29" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="27">
+        <v>1</v>
+      </c>
+      <c r="D7" s="27">
+        <v>1</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="27">
+        <v>1</v>
+      </c>
+      <c r="D8" s="27">
+        <v>2</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="27">
+        <v>2</v>
+      </c>
+      <c r="D9" s="27">
+        <v>1</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="27">
+        <v>2</v>
+      </c>
+      <c r="D10" s="27">
+        <v>1</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A10">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADBB972E-C927-480C-A467-3665FD9F033A}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B2" s="24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>